--- a/personal/biosites/BioSites.xlsx
+++ b/personal/biosites/BioSites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofutah-my.sharepoint.com/personal/u1361811_umail_utah_edu/Documents/00_ShawLabWrapUp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1DA50E1-D8B7-478A-8B94-E42FF78CDD75}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB09D0BE-C0CA-4084-8B05-814D42CA6B8E}"/>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="255" windowWidth="14985" windowHeight="15315" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
+    <workbookView xWindow="-23535" yWindow="1155" windowWidth="21090" windowHeight="12450" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <si>
     <t>Class</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>https://www.ncbi.nlm.nih.gov/protein/</t>
+  </si>
+  <si>
+    <t>https://www.cosmic2.org/</t>
+  </si>
+  <si>
+    <t>Cosmic2</t>
   </si>
 </sst>
 </file>
@@ -244,8 +250,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
     <sortCondition ref="A1:A20"/>
   </sortState>
@@ -555,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643C9F7-9C93-4F11-AC80-950275DBE674}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -783,16 +789,28 @@
         <v>38</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
     <hyperlink ref="C13" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
     <hyperlink ref="C17" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
+    <hyperlink ref="C21" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
--- a/personal/biosites/BioSites.xlsx
+++ b/personal/biosites/BioSites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofutah-my.sharepoint.com/personal/u1361811_umail_utah_edu/Documents/00_ShawLabWrapUp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB09D0BE-C0CA-4084-8B05-814D42CA6B8E}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1F95F97-4A07-42C1-8073-E0D399C38C01}"/>
   <bookViews>
-    <workbookView xWindow="-23535" yWindow="1155" windowWidth="21090" windowHeight="12450" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
+    <workbookView xWindow="-22950" yWindow="930" windowWidth="21090" windowHeight="12450" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>Class</t>
   </si>
@@ -184,6 +184,12 @@
   </si>
   <si>
     <t>Cosmic2</t>
+  </si>
+  <si>
+    <t>https://www.fpbase.org/</t>
+  </si>
+  <si>
+    <t>Fbbase</t>
   </si>
 </sst>
 </file>
@@ -250,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0">
-  <autoFilter ref="A1:C21" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C22" totalsRowShown="0">
+  <autoFilter ref="A1:C22" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
     <sortCondition ref="A1:A20"/>
   </sortState>
@@ -561,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643C9F7-9C93-4F11-AC80-950275DBE674}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -800,6 +806,17 @@
         <v>47</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
@@ -807,10 +824,11 @@
     <hyperlink ref="C13" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
     <hyperlink ref="C17" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
     <hyperlink ref="C21" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
+    <hyperlink ref="C22" r:id="rId6" xr:uid="{4D95AA76-7110-4EDE-9C06-5885F8CABC98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/personal/biosites/BioSites.xlsx
+++ b/personal/biosites/BioSites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofutah-my.sharepoint.com/personal/u1361811_umail_utah_edu/Documents/00_ShawLabWrapUp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1F95F97-4A07-42C1-8073-E0D399C38C01}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5EF36CB-545B-4CFE-BBF3-BAF2189EA4E9}"/>
   <bookViews>
-    <workbookView xWindow="-22950" yWindow="930" windowWidth="21090" windowHeight="12450" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
+    <workbookView xWindow="-30345" yWindow="1635" windowWidth="26985" windowHeight="14820" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>Class</t>
   </si>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>Fbbase</t>
+  </si>
+  <si>
+    <t>https://iupred.elte.hu/</t>
+  </si>
+  <si>
+    <t>AIUPRED</t>
+  </si>
+  <si>
+    <t>https://ilir.warwick.ac.uk/index.php</t>
+  </si>
+  <si>
+    <t>iLIR database</t>
   </si>
 </sst>
 </file>
@@ -256,8 +268,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C22" totalsRowShown="0">
-  <autoFilter ref="A1:C22" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C24" totalsRowShown="0">
+  <autoFilter ref="A1:C24" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
     <sortCondition ref="A1:A20"/>
   </sortState>
@@ -567,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643C9F7-9C93-4F11-AC80-950275DBE674}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -817,6 +829,28 @@
         <v>49</v>
       </c>
     </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
@@ -825,10 +859,12 @@
     <hyperlink ref="C17" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
     <hyperlink ref="C21" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
     <hyperlink ref="C22" r:id="rId6" xr:uid="{4D95AA76-7110-4EDE-9C06-5885F8CABC98}"/>
+    <hyperlink ref="C23" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
+    <hyperlink ref="C24" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/personal/biosites/BioSites.xlsx
+++ b/personal/biosites/BioSites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofutah-my.sharepoint.com/personal/u1361811_umail_utah_edu/Documents/00_ShawLabWrapUp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5EF36CB-545B-4CFE-BBF3-BAF2189EA4E9}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CAF3CCF-D869-4330-AA2A-21CCF386ACB7}"/>
   <bookViews>
-    <workbookView xWindow="-30345" yWindow="1635" windowWidth="26985" windowHeight="14820" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
+    <workbookView xWindow="-27705" yWindow="1440" windowWidth="26985" windowHeight="14820" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>Class</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>iLIR database</t>
+  </si>
+  <si>
+    <t>https://adopt.peptone.io/</t>
+  </si>
+  <si>
+    <t>ADOPT</t>
+  </si>
+  <si>
+    <t>https://prdos.hgc.jp/cgi-bin/top.cgi</t>
+  </si>
+  <si>
+    <t>PrDOS</t>
   </si>
 </sst>
 </file>
@@ -268,10 +280,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C24" totalsRowShown="0">
-  <autoFilter ref="A1:C24" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
-    <sortCondition ref="A1:A20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C26" totalsRowShown="0">
+  <autoFilter ref="A1:C26" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C26">
+    <sortCondition ref="A1:A26"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B59DD689-ECCE-4DB7-AA07-7AE708E42687}" name="Class"/>
@@ -579,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643C9F7-9C93-4F11-AC80-950275DBE674}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -655,46 +667,46 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
+        <v>50</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -702,10 +714,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -713,10 +725,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -724,10 +736,10 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -735,10 +747,10 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -746,10 +758,10 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -757,54 +769,54 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -812,21 +824,21 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -834,37 +846,61 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
-    <hyperlink ref="C9" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
-    <hyperlink ref="C13" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
-    <hyperlink ref="C17" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
-    <hyperlink ref="C21" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
-    <hyperlink ref="C22" r:id="rId6" xr:uid="{4D95AA76-7110-4EDE-9C06-5885F8CABC98}"/>
-    <hyperlink ref="C23" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
-    <hyperlink ref="C24" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
+    <hyperlink ref="C12" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
+    <hyperlink ref="C11" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
+    <hyperlink ref="C15" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
+    <hyperlink ref="C24" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
+    <hyperlink ref="C19" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{4D95AA76-7110-4EDE-9C06-5885F8CABC98}"/>
+    <hyperlink ref="C20" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
+    <hyperlink ref="C21" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
+    <hyperlink ref="C22" r:id="rId9" xr:uid="{56118903-C862-4728-936D-41B6CFC2E930}"/>
+    <hyperlink ref="C23" r:id="rId10" xr:uid="{E3691C3B-5B3E-4F7B-A09D-3AD6FF122602}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
--- a/personal/biosites/BioSites.xlsx
+++ b/personal/biosites/BioSites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofutah-my.sharepoint.com/personal/u1361811_umail_utah_edu/Documents/00_ShawLabWrapUp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CAF3CCF-D869-4330-AA2A-21CCF386ACB7}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BC964C1-2AF9-4FDD-B7BD-9DD3ADF1BCAD}"/>
   <bookViews>
-    <workbookView xWindow="-27705" yWindow="1440" windowWidth="26985" windowHeight="14820" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
+    <workbookView xWindow="-14865" yWindow="765" windowWidth="12540" windowHeight="11070" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
   <si>
     <t>Class</t>
   </si>
@@ -214,6 +214,81 @@
   </si>
   <si>
     <t>PrDOS</t>
+  </si>
+  <si>
+    <t>https://www.biosynth.com/peptide-calculator</t>
+  </si>
+  <si>
+    <t>BIOSYNTH-PeptideCalculator</t>
+  </si>
+  <si>
+    <t>https://www.phosphosite.org/homeAction</t>
+  </si>
+  <si>
+    <t>PhosphoSitePlus</t>
+  </si>
+  <si>
+    <t>CIDER</t>
+  </si>
+  <si>
+    <t>https://pappulab.wustl.edu/CIDER/analysis/</t>
+  </si>
+  <si>
+    <t>https://www.ebi.ac.uk/interpro/</t>
+  </si>
+  <si>
+    <t>InterPro</t>
+  </si>
+  <si>
+    <t>https://smart.embl.de/</t>
+  </si>
+  <si>
+    <t>SMART</t>
+  </si>
+  <si>
+    <t>http://elm.eu.org/</t>
+  </si>
+  <si>
+    <t>ELM</t>
+  </si>
+  <si>
+    <t>https://bioinf.cs.ucl.ac.uk/psipred/</t>
+  </si>
+  <si>
+    <t>FFPred</t>
+  </si>
+  <si>
+    <t>https://perseucpp.ufv.br/run_page</t>
+  </si>
+  <si>
+    <t>PERSEUCPP</t>
+  </si>
+  <si>
+    <t>CCPsite 2.0</t>
+  </si>
+  <si>
+    <t>https://webs.iiitd.edu.in/raghava/cppsite/</t>
+  </si>
+  <si>
+    <t>https://bioinf.cs.ucl.ac.uk/</t>
+  </si>
+  <si>
+    <t>UCL's BIOINF</t>
+  </si>
+  <si>
+    <t>https://animationlab.utah.edu/projects</t>
+  </si>
+  <si>
+    <t>The Animation Lab</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>https://stevewhitten.github.io/Parse_v2_web/</t>
+  </si>
+  <si>
+    <t>ParSe v2</t>
   </si>
 </sst>
 </file>
@@ -280,10 +355,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C26" totalsRowShown="0">
-  <autoFilter ref="A1:C26" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C26">
-    <sortCondition ref="A1:A26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C38" totalsRowShown="0">
+  <autoFilter ref="A1:C38" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C36">
+    <sortCondition ref="A1:A36"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B59DD689-ECCE-4DB7-AA07-7AE708E42687}" name="Class"/>
@@ -591,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643C9F7-9C93-4F11-AC80-950275DBE674}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -678,57 +753,57 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
+        <v>75</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -736,10 +811,10 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -747,10 +822,10 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -758,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -769,10 +844,10 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -780,10 +855,10 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -791,10 +866,10 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -802,10 +877,10 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -813,10 +888,10 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -824,10 +899,10 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,10 +910,10 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -846,61 +921,205 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>27</v>
+        <v>58</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C36" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C12" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
-    <hyperlink ref="C11" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
-    <hyperlink ref="C15" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
-    <hyperlink ref="C24" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
-    <hyperlink ref="C19" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
+    <hyperlink ref="C13" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
+    <hyperlink ref="C17" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
+    <hyperlink ref="C34" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
+    <hyperlink ref="C21" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{4D95AA76-7110-4EDE-9C06-5885F8CABC98}"/>
-    <hyperlink ref="C20" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
-    <hyperlink ref="C21" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
-    <hyperlink ref="C22" r:id="rId9" xr:uid="{56118903-C862-4728-936D-41B6CFC2E930}"/>
-    <hyperlink ref="C23" r:id="rId10" xr:uid="{E3691C3B-5B3E-4F7B-A09D-3AD6FF122602}"/>
+    <hyperlink ref="C22" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
+    <hyperlink ref="C23" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
+    <hyperlink ref="C24" r:id="rId9" xr:uid="{56118903-C862-4728-936D-41B6CFC2E930}"/>
+    <hyperlink ref="C25" r:id="rId10" xr:uid="{E3691C3B-5B3E-4F7B-A09D-3AD6FF122602}"/>
+    <hyperlink ref="C26" r:id="rId11" xr:uid="{5D6B67B1-312E-4961-A7FC-93D94EB546F4}"/>
+    <hyperlink ref="C8" r:id="rId12" xr:uid="{B941AD88-A214-48B9-8D71-1375ECC94E55}"/>
+    <hyperlink ref="C27" r:id="rId13" xr:uid="{DEE9908D-1BC5-444A-88CE-2A91C124077E}"/>
+    <hyperlink ref="C28" r:id="rId14" xr:uid="{C7BDBE86-972E-44C6-AE60-0911BF01DB6C}"/>
+    <hyperlink ref="C29" r:id="rId15" xr:uid="{19C63012-46BB-4CE2-A4A6-8AB4A5B9B526}"/>
+    <hyperlink ref="C30" r:id="rId16" xr:uid="{438CA88F-8F53-4720-B43F-AB957E008269}"/>
+    <hyperlink ref="C31" r:id="rId17" xr:uid="{87F3BDC4-4872-43D7-A41C-E10083482E59}"/>
+    <hyperlink ref="C32" r:id="rId18" xr:uid="{D2A22245-E1B4-4202-9432-4CC851B215B2}"/>
+    <hyperlink ref="C9" r:id="rId19" xr:uid="{DB391247-8F05-4EF5-8FBD-0D77E848455B}"/>
+    <hyperlink ref="C33" r:id="rId20" xr:uid="{3291FBE2-1A79-4BB7-A0A7-0675AD42FCDA}"/>
+    <hyperlink ref="C37" r:id="rId21" xr:uid="{30E0E65F-59E9-4883-B0AD-D5C510AAFCDE}"/>
+    <hyperlink ref="C38" r:id="rId22" xr:uid="{69A2705D-C17B-48CD-B020-82EE2D7DEA47}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
--- a/personal/biosites/BioSites.xlsx
+++ b/personal/biosites/BioSites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofutah-my.sharepoint.com/personal/u1361811_umail_utah_edu/Documents/00_ShawLabWrapUp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BC964C1-2AF9-4FDD-B7BD-9DD3ADF1BCAD}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{E43A19D6-1AB8-4033-96CF-6ADD8A2B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{497D64C1-9A26-493A-B45A-DB734E9DC17E}"/>
   <bookViews>
-    <workbookView xWindow="-14865" yWindow="765" windowWidth="12540" windowHeight="11070" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{1D58BB59-4772-4479-A1DC-FC8865A0ED5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
   <si>
     <t>Class</t>
   </si>
@@ -87,9 +84,6 @@
     <t>https://bio.tools/HawkDock</t>
   </si>
   <si>
-    <t>H++</t>
-  </si>
-  <si>
     <t>Swiss-model</t>
   </si>
   <si>
@@ -138,9 +132,6 @@
     <t>https://www.protpi.ch/</t>
   </si>
   <si>
-    <t>Prot pi</t>
-  </si>
-  <si>
     <t>Haddock</t>
   </si>
   <si>
@@ -237,9 +228,6 @@
     <t>https://www.ebi.ac.uk/interpro/</t>
   </si>
   <si>
-    <t>InterPro</t>
-  </si>
-  <si>
     <t>https://smart.embl.de/</t>
   </si>
   <si>
@@ -249,9 +237,6 @@
     <t>http://elm.eu.org/</t>
   </si>
   <si>
-    <t>ELM</t>
-  </si>
-  <si>
     <t>https://bioinf.cs.ucl.ac.uk/psipred/</t>
   </si>
   <si>
@@ -261,9 +246,6 @@
     <t>https://perseucpp.ufv.br/run_page</t>
   </si>
   <si>
-    <t>PERSEUCPP</t>
-  </si>
-  <si>
     <t>CCPsite 2.0</t>
   </si>
   <si>
@@ -288,7 +270,91 @@
     <t>https://stevewhitten.github.io/Parse_v2_web/</t>
   </si>
   <si>
-    <t>ParSe v2</t>
+    <t>https://nebasechanger.neb.com/</t>
+  </si>
+  <si>
+    <t>NEBaseChanger</t>
+  </si>
+  <si>
+    <t>https://www.uniprot.org/align</t>
+  </si>
+  <si>
+    <t>Align</t>
+  </si>
+  <si>
+    <t>https://nebcloner.neb.com/#!/</t>
+  </si>
+  <si>
+    <t>NEBcloner</t>
+  </si>
+  <si>
+    <t>https://alienlabs.ucd.ie/punch2/</t>
+  </si>
+  <si>
+    <t>PUNCH2</t>
+  </si>
+  <si>
+    <t>https://metapredict.net/</t>
+  </si>
+  <si>
+    <t>metapredict</t>
+  </si>
+  <si>
+    <t>https://slimmine.pbrg.hu/</t>
+  </si>
+  <si>
+    <t>SLiMMine</t>
+  </si>
+  <si>
+    <t>Jalview</t>
+  </si>
+  <si>
+    <t>https://www.jalview.org/</t>
+  </si>
+  <si>
+    <t>https://www.ebi.ac.uk/jdispatcher/msa/clustalo?stype=dna</t>
+  </si>
+  <si>
+    <t>Cluster Omega</t>
+  </si>
+  <si>
+    <t>Sequence Annotation</t>
+  </si>
+  <si>
+    <t>https://www.rcsb.org/alignment</t>
+  </si>
+  <si>
+    <t>Pairwise Structure Alignment</t>
+  </si>
+  <si>
+    <t>Motif Predictions</t>
+  </si>
+  <si>
+    <t>Structure Predictions</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>Comprehensive Tools</t>
+  </si>
+  <si>
+    <t>InterPro (protein classification)</t>
+  </si>
+  <si>
+    <t>ELM (Eukaryotic Linear Motif)</t>
+  </si>
+  <si>
+    <t>ParSe v2 (Phase-separation)</t>
+  </si>
+  <si>
+    <t>PERSEUCPP (Penetrating Peptide)</t>
+  </si>
+  <si>
+    <t>Prot pi (Peptide Features)</t>
+  </si>
+  <si>
+    <t>H++ (pK, pH)</t>
   </si>
 </sst>
 </file>
@@ -354,11 +420,15 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C38" totalsRowShown="0">
-  <autoFilter ref="A1:C38" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C36">
-    <sortCondition ref="A1:A36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}" name="Table1" displayName="Table1" ref="A1:C47" totalsRowShown="0">
+  <autoFilter ref="A1:C47" xr:uid="{B68F6D6F-67EB-476E-9FEE-100B33FCEE2F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C47">
+    <sortCondition ref="A1:A47"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B59DD689-ECCE-4DB7-AA07-7AE708E42687}" name="Class"/>
@@ -370,9 +440,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,7 +480,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -516,7 +586,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -658,7 +728,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -666,15 +736,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643C9F7-9C93-4F11-AC80-950275DBE674}">
-  <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -685,7 +755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -693,10 +763,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -704,10 +774,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -715,10 +785,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -726,10 +796,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -737,389 +807,497 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>9</v>
       </c>
       <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="1" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="1" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>82</v>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
-    <hyperlink ref="C13" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
-    <hyperlink ref="C17" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
-    <hyperlink ref="C34" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
+    <hyperlink ref="C19" r:id="rId1" xr:uid="{F7AD2126-27F5-4930-8637-2C1EFC6B909C}"/>
+    <hyperlink ref="C46" r:id="rId2" xr:uid="{14B8D440-1227-4633-9ABE-332CFC8122A1}"/>
+    <hyperlink ref="C45" r:id="rId3" xr:uid="{EB5E611F-9EBE-4948-851D-30BED8D118BD}"/>
+    <hyperlink ref="C24" r:id="rId4" xr:uid="{622844D9-80C8-4783-B7D9-0717D98EF216}"/>
     <hyperlink ref="C21" r:id="rId5" xr:uid="{1A63E50D-37DC-43ED-9E67-1F534E70FCC0}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{4D95AA76-7110-4EDE-9C06-5885F8CABC98}"/>
-    <hyperlink ref="C22" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
-    <hyperlink ref="C23" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
-    <hyperlink ref="C24" r:id="rId9" xr:uid="{56118903-C862-4728-936D-41B6CFC2E930}"/>
-    <hyperlink ref="C25" r:id="rId10" xr:uid="{E3691C3B-5B3E-4F7B-A09D-3AD6FF122602}"/>
-    <hyperlink ref="C26" r:id="rId11" xr:uid="{5D6B67B1-312E-4961-A7FC-93D94EB546F4}"/>
+    <hyperlink ref="C26" r:id="rId7" xr:uid="{005F180D-C0F3-48E4-A18A-BAC827A0E64D}"/>
+    <hyperlink ref="C38" r:id="rId8" xr:uid="{7A5FEB00-48BA-45D3-A057-7F9088E4644C}"/>
+    <hyperlink ref="C27" r:id="rId9" xr:uid="{56118903-C862-4728-936D-41B6CFC2E930}"/>
+    <hyperlink ref="C28" r:id="rId10" xr:uid="{E3691C3B-5B3E-4F7B-A09D-3AD6FF122602}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{5D6B67B1-312E-4961-A7FC-93D94EB546F4}"/>
     <hyperlink ref="C8" r:id="rId12" xr:uid="{B941AD88-A214-48B9-8D71-1375ECC94E55}"/>
-    <hyperlink ref="C27" r:id="rId13" xr:uid="{DEE9908D-1BC5-444A-88CE-2A91C124077E}"/>
-    <hyperlink ref="C28" r:id="rId14" xr:uid="{C7BDBE86-972E-44C6-AE60-0911BF01DB6C}"/>
-    <hyperlink ref="C29" r:id="rId15" xr:uid="{19C63012-46BB-4CE2-A4A6-8AB4A5B9B526}"/>
-    <hyperlink ref="C30" r:id="rId16" xr:uid="{438CA88F-8F53-4720-B43F-AB957E008269}"/>
-    <hyperlink ref="C31" r:id="rId17" xr:uid="{87F3BDC4-4872-43D7-A41C-E10083482E59}"/>
-    <hyperlink ref="C32" r:id="rId18" xr:uid="{D2A22245-E1B4-4202-9432-4CC851B215B2}"/>
+    <hyperlink ref="C29" r:id="rId13" xr:uid="{DEE9908D-1BC5-444A-88CE-2A91C124077E}"/>
+    <hyperlink ref="C20" r:id="rId14" xr:uid="{C7BDBE86-972E-44C6-AE60-0911BF01DB6C}"/>
+    <hyperlink ref="C35" r:id="rId15" xr:uid="{19C63012-46BB-4CE2-A4A6-8AB4A5B9B526}"/>
+    <hyperlink ref="C36" r:id="rId16" xr:uid="{438CA88F-8F53-4720-B43F-AB957E008269}"/>
+    <hyperlink ref="C22" r:id="rId17" xr:uid="{87F3BDC4-4872-43D7-A41C-E10083482E59}"/>
+    <hyperlink ref="C37" r:id="rId18" xr:uid="{D2A22245-E1B4-4202-9432-4CC851B215B2}"/>
     <hyperlink ref="C9" r:id="rId19" xr:uid="{DB391247-8F05-4EF5-8FBD-0D77E848455B}"/>
-    <hyperlink ref="C33" r:id="rId20" xr:uid="{3291FBE2-1A79-4BB7-A0A7-0675AD42FCDA}"/>
-    <hyperlink ref="C37" r:id="rId21" xr:uid="{30E0E65F-59E9-4883-B0AD-D5C510AAFCDE}"/>
-    <hyperlink ref="C38" r:id="rId22" xr:uid="{69A2705D-C17B-48CD-B020-82EE2D7DEA47}"/>
+    <hyperlink ref="C23" r:id="rId20" xr:uid="{3291FBE2-1A79-4BB7-A0A7-0675AD42FCDA}"/>
+    <hyperlink ref="C40" r:id="rId21" xr:uid="{30E0E65F-59E9-4883-B0AD-D5C510AAFCDE}"/>
+    <hyperlink ref="C30" r:id="rId22" xr:uid="{69A2705D-C17B-48CD-B020-82EE2D7DEA47}"/>
+    <hyperlink ref="C16" r:id="rId23" xr:uid="{ECC9407F-31A4-4DFD-AB37-8157A249A34A}"/>
+    <hyperlink ref="C17" r:id="rId24" xr:uid="{CA7CD3C9-7EA7-457C-B0CA-15B51BB1ABC0}"/>
+    <hyperlink ref="C18" r:id="rId25" location="!/" xr:uid="{E95A21CF-8410-4654-8048-797DF0AFDFB1}"/>
+    <hyperlink ref="C31" r:id="rId26" xr:uid="{673CC9CA-2F89-42EE-9733-92555F3EE4BD}"/>
+    <hyperlink ref="C25" r:id="rId27" xr:uid="{2886A0C2-B41D-4D42-8139-AEC142CA0A71}"/>
+    <hyperlink ref="C39" r:id="rId28" xr:uid="{43317A36-A361-460E-8581-9A8DB7CCCC8C}"/>
+    <hyperlink ref="C42" r:id="rId29" xr:uid="{E4DE48CC-F154-4E20-AAD2-53E3047A48F2}"/>
+    <hyperlink ref="C43" r:id="rId30" xr:uid="{477D0431-14B6-41AB-92F7-CC8BCDD2C336}"/>
+    <hyperlink ref="C41" r:id="rId31" xr:uid="{121EAF92-0CAF-4ACA-989B-31013B356262}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId23"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>